--- a/tools/importer/reports/import-recipe-detail.report.xlsx
+++ b/tools/importer/reports/import-recipe-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="140">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -43,6 +49,9 @@
     <t>["hero-banner","hero-banner","hero-banner"]</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>en</t>
   </si>
   <si>
@@ -82,18 +91,228 @@
     <t>https://www.7up.com/en/recipes</t>
   </si>
   <si>
+    <t>en/recipes/7-7.report.json</t>
+  </si>
+  <si>
+    <t>["hero-recipe","columns-recipe"]</t>
+  </si>
+  <si>
+    <t>en/recipes/7-7</t>
+  </si>
+  <si>
+    <t>recipe-detail</t>
+  </si>
+  <si>
+    <t>2026-09-10T16:24:20.824Z</t>
+  </si>
+  <si>
+    <t>7 &amp; 7 Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7-7</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-biscuits.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-biscuits</t>
+  </si>
+  <si>
+    <t>2026-09-10T16:23:19.337Z</t>
+  </si>
+  <si>
+    <t>7UP® Biscuits Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-biscuits</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-bundt-cake.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-bundt-cake</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:27:51.276Z</t>
+  </si>
+  <si>
+    <t>7UP® Bundt Cake Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-bundt-cake</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-holiday-party-punch.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-holiday-party-punch</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:11:53.226Z</t>
+  </si>
+  <si>
+    <t>7UP® Holiday Party Punch Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-holiday-party-punch</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-mojito.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-mojito</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:23:41.469Z</t>
+  </si>
+  <si>
+    <t>7UP® Mojito Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-mojito</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-rum-rambler.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-rum-rambler</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:51:26.034Z</t>
+  </si>
+  <si>
+    <t>7UP® Rum Rambler Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-rum-rambler</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-sherbet-punch.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-sherbet-punch</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:03:34.559Z</t>
+  </si>
+  <si>
+    <t>7UP® Sherbet Punch | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-sherbet-punch</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-sunrise.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7up-sunrise</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:19:03.760Z</t>
+  </si>
+  <si>
+    <t>7UP® Sunrise Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7up-sunrise</t>
+  </si>
+  <si>
+    <t>en/recipes/7upside-down-cake.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/7upside-down-cake</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:55:23.986Z</t>
+  </si>
+  <si>
+    <t>7UP® Side-Down Cake Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/7upside-down-cake</t>
+  </si>
+  <si>
+    <t>en/recipes/cherry-limeade.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/cherry-limeade</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:25:24.783Z</t>
+  </si>
+  <si>
+    <t>Cherry Limeade Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/cherry-limeade</t>
+  </si>
+  <si>
+    <t>en/recipes/classic-7up-margarita.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/classic-7up-margarita</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:59:40.280Z</t>
+  </si>
+  <si>
+    <t>Classic 7UP Margarita Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/classic-7up-margarita</t>
+  </si>
+  <si>
+    <t>en/recipes/dirty-shirley.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/dirty-shirley</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:23:01.692Z</t>
+  </si>
+  <si>
+    <t>7UP® Dirty Shirley | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/dirty-shirley</t>
+  </si>
+  <si>
+    <t>en/recipes/lemon-lime-float.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/lemon-lime-float</t>
+  </si>
+  <si>
+    <t>2026-09-10T13:51:20.513Z</t>
+  </si>
+  <si>
+    <t>7UP® Lemon Lime Float | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/lemon-lime-float</t>
+  </si>
+  <si>
+    <t>en/recipes/pineapple-sheet-cake.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/pineapple-sheet-cake</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:09:20.595Z</t>
+  </si>
+  <si>
+    <t>Pineapple Sheet Cake Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/pineapple-sheet-cake</t>
+  </si>
+  <si>
     <t>en/recipes/rainbow-sherbet-float.report.json</t>
   </si>
   <si>
-    <t>["hero-recipe","columns-recipe"]</t>
-  </si>
-  <si>
     <t>en/recipes/rainbow-sherbet-float</t>
   </si>
   <si>
-    <t>recipe-detail</t>
-  </si>
-  <si>
     <t>2026-09-10T13:14:38.331Z</t>
   </si>
   <si>
@@ -101,6 +320,119 @@
   </si>
   <si>
     <t>https://www.7up.com/en/recipes/rainbow-sherbet-float</t>
+  </si>
+  <si>
+    <t>en/recipes/shirley-temple-bundt-cake.report.json</t>
+  </si>
+  <si>
+    <t>BLOCKED_PAGE: CLOUDFLARE — "attention required! | cloudflare"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: BLOCKED_PAGE: CLOUDFLARE — "attention required! | cloudflare"
+    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:629:15)
+    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:1012:33)</t>
+  </si>
+  <si>
+    <t>en/recipes/shirley-temple-bundt-cake</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:17:38.838Z</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/shirley-temple-bundt-cake</t>
+  </si>
+  <si>
+    <t>en/recipes/shirley-temple-float.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/shirley-temple-float</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:25:38.990Z</t>
+  </si>
+  <si>
+    <t>7UP® Shirley Temple float | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/shirley-temple-float</t>
+  </si>
+  <si>
+    <t>en/recipes/shirley-temple.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/shirley-temple</t>
+  </si>
+  <si>
+    <t>2026-09-10T14:31:44.194Z</t>
+  </si>
+  <si>
+    <t>Shirley Temple Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/shirley-temple</t>
+  </si>
+  <si>
+    <t>en/recipes/sleigh-bells-and-bubbles.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/sleigh-bells-and-bubbles</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:06:33.273Z</t>
+  </si>
+  <si>
+    <t>Sleigh Bells and Bubbles Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/sleigh-bells-and-bubbles</t>
+  </si>
+  <si>
+    <t>en/recipes/tequila-smash.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/tequila-smash</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:14:52.640Z</t>
+  </si>
+  <si>
+    <t>Tequila Smash Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/tequila-smash</t>
+  </si>
+  <si>
+    <t>en/recipes/tropical-snakebite.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/tropical-snakebite</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:03:44.286Z</t>
+  </si>
+  <si>
+    <t>Tropical Snakebite Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/tropical-snakebite</t>
+  </si>
+  <si>
+    <t>en/recipes/tropical-vacation.report.json</t>
+  </si>
+  <si>
+    <t>en/recipes/tropical-vacation</t>
+  </si>
+  <si>
+    <t>2026-09-10T15:20:49.149Z</t>
+  </si>
+  <si>
+    <t>Tropical Vacation Recipe | 7UP®</t>
+  </si>
+  <si>
+    <t>https://www.7up.com/en/recipes/tropical-vacation</t>
   </si>
 </sst>
 </file>
@@ -489,19 +821,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="3" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,87 +859,783 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>117</v>
+      </c>
+      <c r="I21" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-recipe-detail.report.xlsx
+++ b/tools/importer/reports/import-recipe-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="135">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,12 +19,6 @@
     <t>blocks</t>
   </si>
   <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>errorStack</t>
-  </si>
-  <si>
     <t>path</t>
   </si>
   <si>
@@ -49,9 +43,6 @@
     <t>["hero-banner","hero-banner","hero-banner"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>en</t>
   </si>
   <si>
@@ -325,21 +316,13 @@
     <t>en/recipes/shirley-temple-bundt-cake.report.json</t>
   </si>
   <si>
-    <t>BLOCKED_PAGE: CLOUDFLARE — "attention required! | cloudflare"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: BLOCKED_PAGE: CLOUDFLARE — "attention required! | cloudflare"
-    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:629:15)
-    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:1012:33)</t>
-  </si>
-  <si>
     <t>en/recipes/shirley-temple-bundt-cake</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
-    <t>2026-09-10T14:17:38.838Z</t>
+    <t>2026-09-10T16:26:43.599Z</t>
+  </si>
+  <si>
+    <t>7UP® Shirley Temple Bundt Cake | 7UP®</t>
   </si>
   <si>
     <t>https://www.7up.com/en/recipes/shirley-temple-bundt-cake</t>
@@ -821,20 +804,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,783 +841,633 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="s">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="J5" t="s">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="G6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="J6" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="J7" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="G8" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>49</v>
       </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>50</v>
       </c>
-      <c r="I8" t="s">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="J8" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="G9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>54</v>
       </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>55</v>
       </c>
-      <c r="I9" t="s">
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>56</v>
       </c>
-      <c r="J9" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="G10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
         <v>59</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="I10" t="s">
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
         <v>61</v>
       </c>
-      <c r="J10" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="G11" t="s">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
         <v>64</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>65</v>
       </c>
-      <c r="I11" t="s">
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
         <v>66</v>
       </c>
-      <c r="J11" t="s">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="G12" t="s">
         <v>68</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
         <v>69</v>
       </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>70</v>
       </c>
-      <c r="I12" t="s">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
         <v>71</v>
       </c>
-      <c r="J12" t="s">
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="G13" t="s">
         <v>73</v>
       </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="H13" t="s">
         <v>74</v>
       </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" t="s">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>75</v>
       </c>
-      <c r="I13" t="s">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
         <v>76</v>
       </c>
-      <c r="J13" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="G14" t="s">
         <v>78</v>
       </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="H14" t="s">
         <v>79</v>
       </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" t="s">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>80</v>
       </c>
-      <c r="I14" t="s">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
         <v>81</v>
       </c>
-      <c r="J14" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="G15" t="s">
         <v>83</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="H15" t="s">
         <v>84</v>
       </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" t="s">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>85</v>
       </c>
-      <c r="I15" t="s">
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
         <v>86</v>
       </c>
-      <c r="J15" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="G16" t="s">
         <v>88</v>
       </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="H16" t="s">
         <v>89</v>
       </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" t="s">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>90</v>
       </c>
-      <c r="I16" t="s">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
         <v>91</v>
       </c>
-      <c r="J16" t="s">
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="G17" t="s">
         <v>93</v>
       </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="H17" t="s">
         <v>94</v>
       </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>95</v>
       </c>
-      <c r="I17" t="s">
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
         <v>96</v>
       </c>
-      <c r="J17" t="s">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="G18" t="s">
         <v>98</v>
       </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" t="s">
         <v>99</v>
       </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>100</v>
       </c>
-      <c r="I18" t="s">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
         <v>101</v>
       </c>
-      <c r="J18" t="s">
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="G19" t="s">
         <v>103</v>
       </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="H19" t="s">
         <v>104</v>
       </c>
-      <c r="D19" t="s">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>105</v>
       </c>
-      <c r="E19" t="s">
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
         <v>106</v>
       </c>
-      <c r="F19" t="s">
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="G19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="G20" t="s">
         <v>108</v>
       </c>
-      <c r="I19" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="H20" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>110</v>
       </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
         <v>111</v>
       </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
         <v>112</v>
       </c>
-      <c r="I20" t="s">
+      <c r="G21" t="s">
         <v>113</v>
       </c>
-      <c r="J20" t="s">
+      <c r="H21" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>115</v>
       </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
         <v>116</v>
       </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
         <v>117</v>
       </c>
-      <c r="I21" t="s">
+      <c r="G22" t="s">
         <v>118</v>
       </c>
-      <c r="J21" t="s">
+      <c r="H22" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>120</v>
       </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
         <v>121</v>
       </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
         <v>122</v>
       </c>
-      <c r="I22" t="s">
+      <c r="G23" t="s">
         <v>123</v>
       </c>
-      <c r="J22" t="s">
+      <c r="H23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>125</v>
       </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
         <v>126</v>
       </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
         <v>127</v>
       </c>
-      <c r="I23" t="s">
+      <c r="G24" t="s">
         <v>128</v>
       </c>
-      <c r="J23" t="s">
+      <c r="H24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>130</v>
       </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
         <v>131</v>
       </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
         <v>132</v>
       </c>
-      <c r="I24" t="s">
+      <c r="G25" t="s">
         <v>133</v>
       </c>
-      <c r="J24" t="s">
+      <c r="H25" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" t="s">
-        <v>138</v>
-      </c>
-      <c r="J25" t="s">
-        <v>139</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-recipe-detail.report.xlsx
+++ b/tools/importer/reports/import-recipe-detail.report.xlsx
@@ -73,7 +73,7 @@
     <t>recipes</t>
   </si>
   <si>
-    <t>2026-09-09T19:01:05.695Z</t>
+    <t>2026-09-10T17:56:50.300Z</t>
   </si>
   <si>
     <t>7UP® Recipes | 7up.com</t>
@@ -184,7 +184,7 @@
     <t>en/recipes/7up-sherbet-punch</t>
   </si>
   <si>
-    <t>2026-09-10T14:03:34.559Z</t>
+    <t>2026-09-10T18:06:29.450Z</t>
   </si>
   <si>
     <t>7UP® Sherbet Punch | 7UP®</t>
@@ -259,7 +259,7 @@
     <t>en/recipes/dirty-shirley</t>
   </si>
   <si>
-    <t>2026-09-10T14:23:01.692Z</t>
+    <t>2026-09-10T18:04:18.884Z</t>
   </si>
   <si>
     <t>7UP® Dirty Shirley | 7UP®</t>
@@ -274,7 +274,7 @@
     <t>en/recipes/lemon-lime-float</t>
   </si>
   <si>
-    <t>2026-09-10T13:51:20.513Z</t>
+    <t>2026-09-10T18:06:09.337Z</t>
   </si>
   <si>
     <t>7UP® Lemon Lime Float | 7UP®</t>
@@ -304,7 +304,7 @@
     <t>en/recipes/rainbow-sherbet-float</t>
   </si>
   <si>
-    <t>2026-09-10T13:14:38.331Z</t>
+    <t>2026-09-10T18:06:54.403Z</t>
   </si>
   <si>
     <t>7UP® Rainbow Sherbet Float | 7UP®</t>
@@ -334,7 +334,7 @@
     <t>en/recipes/shirley-temple-float</t>
   </si>
   <si>
-    <t>2026-09-10T14:25:38.990Z</t>
+    <t>2026-09-10T18:04:41.517Z</t>
   </si>
   <si>
     <t>7UP® Shirley Temple float | 7UP®</t>
@@ -349,7 +349,7 @@
     <t>en/recipes/shirley-temple</t>
   </si>
   <si>
-    <t>2026-09-10T14:31:44.194Z</t>
+    <t>2026-09-10T18:05:49.061Z</t>
   </si>
   <si>
     <t>Shirley Temple Recipe | 7UP®</t>
